--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130341272</v>
+        <v>130341273</v>
       </c>
       <c r="B2" t="n">
         <v>79180</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482934</v>
+        <v>483056</v>
       </c>
       <c r="R2" t="n">
-        <v>6989813</v>
+        <v>6989618</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130341273</v>
+        <v>130341272</v>
       </c>
       <c r="B3" t="n">
         <v>79180</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483056</v>
+        <v>482934</v>
       </c>
       <c r="R3" t="n">
-        <v>6989618</v>
+        <v>6989813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130341250</v>
+        <v>130341253</v>
       </c>
       <c r="B9" t="n">
         <v>57826</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482916</v>
+        <v>483089</v>
       </c>
       <c r="R9" t="n">
-        <v>6989870</v>
+        <v>6989585</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Lockne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,7 +1461,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130341253</v>
+        <v>130341250</v>
       </c>
       <c r="B10" t="n">
         <v>57826</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483089</v>
+        <v>482916</v>
       </c>
       <c r="R10" t="n">
-        <v>6989585</v>
+        <v>6989870</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Lockne</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341249</v>
+        <v>130341239</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482941</v>
+        <v>482925</v>
       </c>
       <c r="R11" t="n">
-        <v>6989821</v>
+        <v>6989758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341239</v>
+        <v>130341249</v>
       </c>
       <c r="B12" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482925</v>
+        <v>482941</v>
       </c>
       <c r="R12" t="n">
-        <v>6989758</v>
+        <v>6989821</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1731,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2155,7 +2155,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130341259</v>
+        <v>130341257</v>
       </c>
       <c r="B17" t="n">
         <v>80285</v>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483019</v>
+        <v>483028</v>
       </c>
       <c r="R17" t="n">
-        <v>6989574</v>
+        <v>6989627</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130341257</v>
+        <v>130341259</v>
       </c>
       <c r="B19" t="n">
         <v>80285</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483028</v>
+        <v>483019</v>
       </c>
       <c r="R19" t="n">
-        <v>6989627</v>
+        <v>6989574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341248</v>
+        <v>130341258</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482985</v>
+        <v>483022</v>
       </c>
       <c r="R22" t="n">
-        <v>6989751</v>
+        <v>6989613</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2711,11 +2711,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2839,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341258</v>
+        <v>130341248</v>
       </c>
       <c r="B24" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2845,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483022</v>
+        <v>482985</v>
       </c>
       <c r="R24" t="n">
-        <v>6989613</v>
+        <v>6989751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,6 +2905,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130341241</v>
+        <v>130341275</v>
       </c>
       <c r="B26" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482982</v>
+        <v>483003</v>
       </c>
       <c r="R26" t="n">
-        <v>6989699</v>
+        <v>6989510</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130341275</v>
+        <v>130341241</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483003</v>
+        <v>482982</v>
       </c>
       <c r="R27" t="n">
-        <v>6989510</v>
+        <v>6989699</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R28" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B29" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R29" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341239</v>
+        <v>130341249</v>
       </c>
       <c r="B11" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482925</v>
+        <v>482941</v>
       </c>
       <c r="R11" t="n">
-        <v>6989758</v>
+        <v>6989821</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341249</v>
+        <v>130341239</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482941</v>
+        <v>482925</v>
       </c>
       <c r="R12" t="n">
-        <v>6989821</v>
+        <v>6989758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341267</v>
+        <v>130341247</v>
       </c>
       <c r="B15" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482997</v>
+        <v>482995</v>
       </c>
       <c r="R15" t="n">
-        <v>6989532</v>
+        <v>6989739</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2027,6 +2027,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R16" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341258</v>
+        <v>130341274</v>
       </c>
       <c r="B22" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483022</v>
+        <v>483054</v>
       </c>
       <c r="R22" t="n">
-        <v>6989613</v>
+        <v>6989557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341274</v>
+        <v>130341258</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483054</v>
+        <v>483022</v>
       </c>
       <c r="R23" t="n">
-        <v>6989557</v>
+        <v>6989613</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B7" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R7" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R8" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341269</v>
+        <v>130341247</v>
       </c>
       <c r="B14" t="n">
-        <v>91724</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483005</v>
+        <v>482995</v>
       </c>
       <c r="R14" t="n">
-        <v>6989508</v>
+        <v>6989739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1930,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341267</v>
+        <v>130341269</v>
       </c>
       <c r="B15" t="n">
-        <v>80285</v>
+        <v>91724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482997</v>
+        <v>483005</v>
       </c>
       <c r="R15" t="n">
-        <v>6989532</v>
+        <v>6989508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R16" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341247</v>
+        <v>130341269</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>91724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482995</v>
+        <v>483005</v>
       </c>
       <c r="R14" t="n">
-        <v>6989739</v>
+        <v>6989508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1961,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341269</v>
+        <v>130341267</v>
       </c>
       <c r="B15" t="n">
-        <v>91724</v>
+        <v>80285</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483005</v>
+        <v>482997</v>
       </c>
       <c r="R15" t="n">
-        <v>6989508</v>
+        <v>6989532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341267</v>
+        <v>130341247</v>
       </c>
       <c r="B16" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482997</v>
+        <v>482995</v>
       </c>
       <c r="R16" t="n">
-        <v>6989532</v>
+        <v>6989739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R28" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B29" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R29" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R7" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B8" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R8" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341269</v>
+        <v>130341247</v>
       </c>
       <c r="B14" t="n">
-        <v>91724</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483005</v>
+        <v>482995</v>
       </c>
       <c r="R14" t="n">
-        <v>6989508</v>
+        <v>6989739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1930,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341267</v>
+        <v>130341269</v>
       </c>
       <c r="B15" t="n">
-        <v>80285</v>
+        <v>91724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482997</v>
+        <v>483005</v>
       </c>
       <c r="R15" t="n">
-        <v>6989532</v>
+        <v>6989508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R16" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130341241</v>
+        <v>130341275</v>
       </c>
       <c r="B26" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482982</v>
+        <v>483003</v>
       </c>
       <c r="R26" t="n">
-        <v>6989699</v>
+        <v>6989510</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130341275</v>
+        <v>130341241</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483003</v>
+        <v>482982</v>
       </c>
       <c r="R27" t="n">
-        <v>6989510</v>
+        <v>6989699</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130341273</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130341272</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130341240</v>
       </c>
       <c r="B4" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130341260</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>130341261</v>
       </c>
       <c r="B7" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>130341271</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130341239</v>
       </c>
       <c r="B11" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>130341264</v>
       </c>
       <c r="B13" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>80288</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R14" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1964,7 +1959,7 @@
         <v>130341269</v>
       </c>
       <c r="B15" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341267</v>
+        <v>130341247</v>
       </c>
       <c r="B16" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482997</v>
+        <v>482995</v>
       </c>
       <c r="R16" t="n">
-        <v>6989532</v>
+        <v>6989739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,7 +2158,7 @@
         <v>130341257</v>
       </c>
       <c r="B17" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>130341262</v>
       </c>
       <c r="B18" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>130341259</v>
       </c>
       <c r="B19" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>130341265</v>
       </c>
       <c r="B20" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130341268</v>
       </c>
       <c r="B21" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341248</v>
+        <v>130341258</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>80288</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482985</v>
+        <v>483022</v>
       </c>
       <c r="R22" t="n">
-        <v>6989751</v>
+        <v>6989613</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2711,11 +2711,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341258</v>
+        <v>130341274</v>
       </c>
       <c r="B23" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483022</v>
+        <v>483054</v>
       </c>
       <c r="R23" t="n">
-        <v>6989613</v>
+        <v>6989557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341274</v>
+        <v>130341248</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2845,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483054</v>
+        <v>482985</v>
       </c>
       <c r="R24" t="n">
-        <v>6989557</v>
+        <v>6989751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,6 +2905,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,7 +2939,7 @@
         <v>130341266</v>
       </c>
       <c r="B25" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>130341275</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>130341241</v>
       </c>
       <c r="B27" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B28" t="n">
-        <v>91728</v>
+        <v>79183</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R28" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>91731</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R29" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3531,7 +3531,7 @@
         <v>130341263</v>
       </c>
       <c r="B31" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130341273</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130341272</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130341240</v>
       </c>
       <c r="B4" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130341260</v>
       </c>
       <c r="B5" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130341252</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B7" t="n">
-        <v>80288</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R7" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>80314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R8" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
         <v>130341253</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130341250</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130341239</v>
       </c>
       <c r="B11" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>130341249</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>130341264</v>
       </c>
       <c r="B13" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341267</v>
+        <v>130341247</v>
       </c>
       <c r="B14" t="n">
-        <v>80288</v>
+        <v>57852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482997</v>
+        <v>482995</v>
       </c>
       <c r="R14" t="n">
-        <v>6989532</v>
+        <v>6989739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1930,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341269</v>
+        <v>130341267</v>
       </c>
       <c r="B15" t="n">
-        <v>91727</v>
+        <v>80314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483005</v>
+        <v>482997</v>
       </c>
       <c r="R15" t="n">
-        <v>6989508</v>
+        <v>6989532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341247</v>
+        <v>130341269</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>91753</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482995</v>
+        <v>483005</v>
       </c>
       <c r="R16" t="n">
-        <v>6989739</v>
+        <v>6989508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,7 +2158,7 @@
         <v>130341257</v>
       </c>
       <c r="B17" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>130341262</v>
       </c>
       <c r="B18" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>130341259</v>
       </c>
       <c r="B19" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>130341265</v>
       </c>
       <c r="B20" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130341268</v>
       </c>
       <c r="B21" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>130341258</v>
       </c>
       <c r="B22" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341274</v>
+        <v>130341248</v>
       </c>
       <c r="B23" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483054</v>
+        <v>482985</v>
       </c>
       <c r="R23" t="n">
-        <v>6989557</v>
+        <v>6989751</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,6 +2808,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341248</v>
+        <v>130341274</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482985</v>
+        <v>483054</v>
       </c>
       <c r="R24" t="n">
-        <v>6989751</v>
+        <v>6989557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2905,11 +2910,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,7 +2939,7 @@
         <v>130341266</v>
       </c>
       <c r="B25" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130341275</v>
+        <v>130341241</v>
       </c>
       <c r="B26" t="n">
-        <v>79183</v>
+        <v>91757</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483003</v>
+        <v>482982</v>
       </c>
       <c r="R26" t="n">
-        <v>6989510</v>
+        <v>6989699</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130341241</v>
+        <v>130341275</v>
       </c>
       <c r="B27" t="n">
-        <v>91731</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482982</v>
+        <v>483003</v>
       </c>
       <c r="R27" t="n">
-        <v>6989699</v>
+        <v>6989510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B28" t="n">
-        <v>79183</v>
+        <v>91757</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R28" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B29" t="n">
-        <v>91731</v>
+        <v>79209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R29" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3429,7 +3429,7 @@
         <v>130341254</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>130341263</v>
       </c>
       <c r="B31" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>130341251</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R7" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B8" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R8" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341258</v>
+        <v>130341274</v>
       </c>
       <c r="B22" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483022</v>
+        <v>483054</v>
       </c>
       <c r="R22" t="n">
-        <v>6989613</v>
+        <v>6989557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341248</v>
+        <v>130341258</v>
       </c>
       <c r="B23" t="n">
-        <v>57852</v>
+        <v>80314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482985</v>
+        <v>483022</v>
       </c>
       <c r="R23" t="n">
-        <v>6989751</v>
+        <v>6989613</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,11 +2808,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341274</v>
+        <v>130341248</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2845,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483054</v>
+        <v>482985</v>
       </c>
       <c r="R24" t="n">
-        <v>6989557</v>
+        <v>6989751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,6 +2905,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>130341240</v>
       </c>
       <c r="B4" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B7" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R7" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R8" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
         <v>130341239</v>
       </c>
       <c r="B11" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B14" t="n">
-        <v>57852</v>
+        <v>80314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R14" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1961,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341267</v>
+        <v>130341269</v>
       </c>
       <c r="B15" t="n">
-        <v>80314</v>
+        <v>91754</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482997</v>
+        <v>483005</v>
       </c>
       <c r="R15" t="n">
-        <v>6989532</v>
+        <v>6989508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341269</v>
+        <v>130341247</v>
       </c>
       <c r="B16" t="n">
-        <v>91753</v>
+        <v>57852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483005</v>
+        <v>482995</v>
       </c>
       <c r="R16" t="n">
-        <v>6989508</v>
+        <v>6989739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3036,7 +3036,7 @@
         <v>130341241</v>
       </c>
       <c r="B26" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>130341242</v>
       </c>
       <c r="B28" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>130341240</v>
       </c>
       <c r="B4" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R7" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B8" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R8" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341239</v>
+        <v>130341249</v>
       </c>
       <c r="B11" t="n">
-        <v>91758</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482925</v>
+        <v>482941</v>
       </c>
       <c r="R11" t="n">
-        <v>6989758</v>
+        <v>6989821</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341249</v>
+        <v>130341239</v>
       </c>
       <c r="B12" t="n">
-        <v>57852</v>
+        <v>91759</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482941</v>
+        <v>482925</v>
       </c>
       <c r="R12" t="n">
-        <v>6989821</v>
+        <v>6989758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341267</v>
+        <v>130341247</v>
       </c>
       <c r="B14" t="n">
-        <v>80314</v>
+        <v>57852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482997</v>
+        <v>482995</v>
       </c>
       <c r="R14" t="n">
-        <v>6989532</v>
+        <v>6989739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1930,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1959,7 +1964,7 @@
         <v>130341269</v>
       </c>
       <c r="B15" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B16" t="n">
-        <v>57852</v>
+        <v>80314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R16" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,7 +2155,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130341257</v>
+        <v>130341262</v>
       </c>
       <c r="B17" t="n">
         <v>80314</v>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483028</v>
+        <v>483057</v>
       </c>
       <c r="R17" t="n">
-        <v>6989627</v>
+        <v>6989643</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130341262</v>
+        <v>130341257</v>
       </c>
       <c r="B18" t="n">
         <v>80314</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483057</v>
+        <v>483028</v>
       </c>
       <c r="R18" t="n">
-        <v>6989643</v>
+        <v>6989627</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341274</v>
+        <v>130341258</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483054</v>
+        <v>483022</v>
       </c>
       <c r="R22" t="n">
-        <v>6989557</v>
+        <v>6989613</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341258</v>
+        <v>130341248</v>
       </c>
       <c r="B23" t="n">
-        <v>80314</v>
+        <v>57852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483022</v>
+        <v>482985</v>
       </c>
       <c r="R23" t="n">
-        <v>6989613</v>
+        <v>6989751</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,6 +2808,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341248</v>
+        <v>130341274</v>
       </c>
       <c r="B24" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482985</v>
+        <v>483054</v>
       </c>
       <c r="R24" t="n">
-        <v>6989751</v>
+        <v>6989557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2905,11 +2910,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3036,7 +3036,7 @@
         <v>130341241</v>
       </c>
       <c r="B26" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B28" t="n">
-        <v>91758</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R28" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B29" t="n">
-        <v>79209</v>
+        <v>91759</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R29" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130341273</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130341272</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130341240</v>
       </c>
       <c r="B4" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130341260</v>
       </c>
       <c r="B5" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130341252</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B7" t="n">
-        <v>80314</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R7" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>80316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R8" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
         <v>130341253</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130341250</v>
       </c>
       <c r="B10" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341249</v>
+        <v>130341239</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>91761</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482941</v>
+        <v>482925</v>
       </c>
       <c r="R11" t="n">
-        <v>6989821</v>
+        <v>6989758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341239</v>
+        <v>130341249</v>
       </c>
       <c r="B12" t="n">
-        <v>91759</v>
+        <v>57854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482925</v>
+        <v>482941</v>
       </c>
       <c r="R12" t="n">
-        <v>6989758</v>
+        <v>6989821</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1731,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1765,7 +1765,7 @@
         <v>130341264</v>
       </c>
       <c r="B13" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B14" t="n">
-        <v>57852</v>
+        <v>80316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R14" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1961,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341269</v>
+        <v>130341247</v>
       </c>
       <c r="B15" t="n">
-        <v>91755</v>
+        <v>57854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483005</v>
+        <v>482995</v>
       </c>
       <c r="R15" t="n">
-        <v>6989508</v>
+        <v>6989739</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2032,6 +2027,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341267</v>
+        <v>130341269</v>
       </c>
       <c r="B16" t="n">
-        <v>80314</v>
+        <v>91757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482997</v>
+        <v>483005</v>
       </c>
       <c r="R16" t="n">
-        <v>6989532</v>
+        <v>6989508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130341262</v>
+        <v>130341257</v>
       </c>
       <c r="B17" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483057</v>
+        <v>483028</v>
       </c>
       <c r="R17" t="n">
-        <v>6989643</v>
+        <v>6989627</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130341257</v>
+        <v>130341262</v>
       </c>
       <c r="B18" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483028</v>
+        <v>483057</v>
       </c>
       <c r="R18" t="n">
-        <v>6989627</v>
+        <v>6989643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,7 +2352,7 @@
         <v>130341259</v>
       </c>
       <c r="B19" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>130341265</v>
       </c>
       <c r="B20" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130341268</v>
       </c>
       <c r="B21" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341258</v>
+        <v>130341274</v>
       </c>
       <c r="B22" t="n">
-        <v>80314</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483022</v>
+        <v>483054</v>
       </c>
       <c r="R22" t="n">
-        <v>6989613</v>
+        <v>6989557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341248</v>
+        <v>130341258</v>
       </c>
       <c r="B23" t="n">
-        <v>57852</v>
+        <v>80316</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482985</v>
+        <v>483022</v>
       </c>
       <c r="R23" t="n">
-        <v>6989751</v>
+        <v>6989613</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,11 +2808,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341274</v>
+        <v>130341248</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2845,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483054</v>
+        <v>482985</v>
       </c>
       <c r="R24" t="n">
-        <v>6989557</v>
+        <v>6989751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,6 +2905,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,7 +2939,7 @@
         <v>130341266</v>
       </c>
       <c r="B25" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>130341241</v>
       </c>
       <c r="B26" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>130341275</v>
       </c>
       <c r="B27" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B28" t="n">
-        <v>79209</v>
+        <v>91761</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R28" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B29" t="n">
-        <v>91759</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R29" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3429,7 +3429,7 @@
         <v>130341254</v>
       </c>
       <c r="B30" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>130341263</v>
       </c>
       <c r="B31" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>130341251</v>
       </c>
       <c r="B32" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R7" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B8" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R8" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341267</v>
+        <v>130341269</v>
       </c>
       <c r="B14" t="n">
-        <v>80316</v>
+        <v>91757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482997</v>
+        <v>483005</v>
       </c>
       <c r="R14" t="n">
-        <v>6989532</v>
+        <v>6989508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B15" t="n">
-        <v>57854</v>
+        <v>80316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R15" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2027,11 +2027,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341269</v>
+        <v>130341247</v>
       </c>
       <c r="B16" t="n">
-        <v>91757</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483005</v>
+        <v>482995</v>
       </c>
       <c r="R16" t="n">
-        <v>6989508</v>
+        <v>6989739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341274</v>
+        <v>130341258</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483054</v>
+        <v>483022</v>
       </c>
       <c r="R22" t="n">
-        <v>6989557</v>
+        <v>6989613</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341258</v>
+        <v>130341274</v>
       </c>
       <c r="B23" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483022</v>
+        <v>483054</v>
       </c>
       <c r="R23" t="n">
-        <v>6989613</v>
+        <v>6989557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130341273</v>
+        <v>130341272</v>
       </c>
       <c r="B2" t="n">
         <v>79211</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483056</v>
+        <v>482934</v>
       </c>
       <c r="R2" t="n">
-        <v>6989618</v>
+        <v>6989813</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130341272</v>
+        <v>130341273</v>
       </c>
       <c r="B3" t="n">
         <v>79211</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482934</v>
+        <v>483056</v>
       </c>
       <c r="R3" t="n">
-        <v>6989813</v>
+        <v>6989618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B7" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R7" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R8" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341269</v>
+        <v>130341247</v>
       </c>
       <c r="B14" t="n">
-        <v>91757</v>
+        <v>57854</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483005</v>
+        <v>482995</v>
       </c>
       <c r="R14" t="n">
-        <v>6989508</v>
+        <v>6989739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1930,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341267</v>
+        <v>130341269</v>
       </c>
       <c r="B15" t="n">
-        <v>80316</v>
+        <v>91757</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482997</v>
+        <v>483005</v>
       </c>
       <c r="R15" t="n">
-        <v>6989532</v>
+        <v>6989508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>80316</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R16" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341258</v>
+        <v>130341274</v>
       </c>
       <c r="B22" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483022</v>
+        <v>483054</v>
       </c>
       <c r="R22" t="n">
-        <v>6989613</v>
+        <v>6989557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341274</v>
+        <v>130341248</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483054</v>
+        <v>482985</v>
       </c>
       <c r="R23" t="n">
-        <v>6989557</v>
+        <v>6989751</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,6 +2808,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341248</v>
+        <v>130341258</v>
       </c>
       <c r="B24" t="n">
-        <v>57854</v>
+        <v>80316</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482985</v>
+        <v>483022</v>
       </c>
       <c r="R24" t="n">
-        <v>6989751</v>
+        <v>6989613</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2905,11 +2910,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R7" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B8" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R8" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341247</v>
+        <v>130341269</v>
       </c>
       <c r="B14" t="n">
-        <v>57854</v>
+        <v>91757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482995</v>
+        <v>483005</v>
       </c>
       <c r="R14" t="n">
-        <v>6989739</v>
+        <v>6989508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1961,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341269</v>
+        <v>130341247</v>
       </c>
       <c r="B15" t="n">
-        <v>91757</v>
+        <v>57854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483005</v>
+        <v>482995</v>
       </c>
       <c r="R15" t="n">
-        <v>6989508</v>
+        <v>6989739</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2032,6 +2027,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341274</v>
+        <v>130341258</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483054</v>
+        <v>483022</v>
       </c>
       <c r="R22" t="n">
-        <v>6989557</v>
+        <v>6989613</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341248</v>
+        <v>130341274</v>
       </c>
       <c r="B23" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482985</v>
+        <v>483054</v>
       </c>
       <c r="R23" t="n">
-        <v>6989751</v>
+        <v>6989557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,11 +2808,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341258</v>
+        <v>130341248</v>
       </c>
       <c r="B24" t="n">
-        <v>80316</v>
+        <v>57854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2845,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483022</v>
+        <v>482985</v>
       </c>
       <c r="R24" t="n">
-        <v>6989613</v>
+        <v>6989751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,6 +2905,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130341272</v>
+        <v>130341273</v>
       </c>
       <c r="B2" t="n">
         <v>79211</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482934</v>
+        <v>483056</v>
       </c>
       <c r="R2" t="n">
-        <v>6989813</v>
+        <v>6989618</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130341273</v>
+        <v>130341272</v>
       </c>
       <c r="B3" t="n">
         <v>79211</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483056</v>
+        <v>482934</v>
       </c>
       <c r="R3" t="n">
-        <v>6989618</v>
+        <v>6989813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B7" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R7" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R8" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B15" t="n">
-        <v>57854</v>
+        <v>80316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R15" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2027,11 +2027,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341267</v>
+        <v>130341247</v>
       </c>
       <c r="B16" t="n">
-        <v>80316</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482997</v>
+        <v>482995</v>
       </c>
       <c r="R16" t="n">
-        <v>6989532</v>
+        <v>6989739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341258</v>
+        <v>130341274</v>
       </c>
       <c r="B22" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483022</v>
+        <v>483054</v>
       </c>
       <c r="R22" t="n">
-        <v>6989613</v>
+        <v>6989557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341274</v>
+        <v>130341258</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483054</v>
+        <v>483022</v>
       </c>
       <c r="R23" t="n">
-        <v>6989557</v>
+        <v>6989613</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130341241</v>
+        <v>130341275</v>
       </c>
       <c r="B26" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482982</v>
+        <v>483003</v>
       </c>
       <c r="R26" t="n">
-        <v>6989699</v>
+        <v>6989510</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130341275</v>
+        <v>130341241</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483003</v>
+        <v>482982</v>
       </c>
       <c r="R27" t="n">
-        <v>6989510</v>
+        <v>6989699</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B28" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R28" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R29" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130341273</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130341272</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130341240</v>
       </c>
       <c r="B4" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130341260</v>
       </c>
       <c r="B5" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130341252</v>
       </c>
       <c r="B6" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>80324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R7" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B8" t="n">
-        <v>80316</v>
+        <v>79219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R8" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
         <v>130341253</v>
       </c>
       <c r="B9" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130341250</v>
       </c>
       <c r="B10" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130341239</v>
       </c>
       <c r="B11" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>130341249</v>
       </c>
       <c r="B12" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>130341264</v>
       </c>
       <c r="B13" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341269</v>
+        <v>130341247</v>
       </c>
       <c r="B14" t="n">
-        <v>91757</v>
+        <v>57862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483005</v>
+        <v>482995</v>
       </c>
       <c r="R14" t="n">
-        <v>6989508</v>
+        <v>6989739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1930,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341267</v>
+        <v>130341269</v>
       </c>
       <c r="B15" t="n">
-        <v>80316</v>
+        <v>91770</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482997</v>
+        <v>483005</v>
       </c>
       <c r="R15" t="n">
-        <v>6989532</v>
+        <v>6989508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>80324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R16" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,7 +2158,7 @@
         <v>130341257</v>
       </c>
       <c r="B17" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130341262</v>
+        <v>130341259</v>
       </c>
       <c r="B18" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483057</v>
+        <v>483019</v>
       </c>
       <c r="R18" t="n">
-        <v>6989643</v>
+        <v>6989574</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130341259</v>
+        <v>130341262</v>
       </c>
       <c r="B19" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483019</v>
+        <v>483057</v>
       </c>
       <c r="R19" t="n">
-        <v>6989574</v>
+        <v>6989643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
         <v>130341265</v>
       </c>
       <c r="B20" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130341268</v>
       </c>
       <c r="B21" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341274</v>
+        <v>130341248</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483054</v>
+        <v>482985</v>
       </c>
       <c r="R22" t="n">
-        <v>6989557</v>
+        <v>6989751</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2711,6 +2711,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2740,7 +2745,7 @@
         <v>130341258</v>
       </c>
       <c r="B23" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2834,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341248</v>
+        <v>130341274</v>
       </c>
       <c r="B24" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482985</v>
+        <v>483054</v>
       </c>
       <c r="R24" t="n">
-        <v>6989751</v>
+        <v>6989557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2905,11 +2910,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,7 +2939,7 @@
         <v>130341266</v>
       </c>
       <c r="B25" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130341275</v>
+        <v>130341241</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>91774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483003</v>
+        <v>482982</v>
       </c>
       <c r="R26" t="n">
-        <v>6989510</v>
+        <v>6989699</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130341241</v>
+        <v>130341275</v>
       </c>
       <c r="B27" t="n">
-        <v>91761</v>
+        <v>79219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482982</v>
+        <v>483003</v>
       </c>
       <c r="R27" t="n">
-        <v>6989699</v>
+        <v>6989510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>91774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R28" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B29" t="n">
-        <v>91761</v>
+        <v>79219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R29" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3429,7 +3429,7 @@
         <v>130341254</v>
       </c>
       <c r="B30" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>130341263</v>
       </c>
       <c r="B31" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>130341251</v>
       </c>
       <c r="B32" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130341273</v>
+        <v>130341272</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483056</v>
+        <v>482934</v>
       </c>
       <c r="R2" t="n">
-        <v>6989618</v>
+        <v>6989813</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130341272</v>
+        <v>130341273</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482934</v>
+        <v>483056</v>
       </c>
       <c r="R3" t="n">
-        <v>6989813</v>
+        <v>6989618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>130341240</v>
       </c>
       <c r="B4" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130341260</v>
       </c>
       <c r="B5" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130341252</v>
       </c>
       <c r="B6" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B7" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R7" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>80325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R8" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
         <v>130341253</v>
       </c>
       <c r="B9" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130341250</v>
       </c>
       <c r="B10" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130341239</v>
       </c>
       <c r="B11" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>130341249</v>
       </c>
       <c r="B12" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>130341264</v>
       </c>
       <c r="B13" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341247</v>
+        <v>130341269</v>
       </c>
       <c r="B14" t="n">
-        <v>57862</v>
+        <v>91771</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482995</v>
+        <v>483005</v>
       </c>
       <c r="R14" t="n">
-        <v>6989739</v>
+        <v>6989508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1961,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341269</v>
+        <v>130341247</v>
       </c>
       <c r="B15" t="n">
-        <v>91770</v>
+        <v>57863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483005</v>
+        <v>482995</v>
       </c>
       <c r="R15" t="n">
-        <v>6989508</v>
+        <v>6989739</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2032,6 +2027,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2061,7 +2061,7 @@
         <v>130341267</v>
       </c>
       <c r="B16" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>130341257</v>
       </c>
       <c r="B17" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130341259</v>
+        <v>130341262</v>
       </c>
       <c r="B18" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483019</v>
+        <v>483057</v>
       </c>
       <c r="R18" t="n">
-        <v>6989574</v>
+        <v>6989643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130341262</v>
+        <v>130341259</v>
       </c>
       <c r="B19" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483057</v>
+        <v>483019</v>
       </c>
       <c r="R19" t="n">
-        <v>6989643</v>
+        <v>6989574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
         <v>130341265</v>
       </c>
       <c r="B20" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130341268</v>
       </c>
       <c r="B21" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341248</v>
+        <v>130341274</v>
       </c>
       <c r="B22" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>482985</v>
+        <v>483054</v>
       </c>
       <c r="R22" t="n">
-        <v>6989751</v>
+        <v>6989557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2711,11 +2711,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2745,7 +2740,7 @@
         <v>130341258</v>
       </c>
       <c r="B23" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2839,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341274</v>
+        <v>130341248</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2845,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483054</v>
+        <v>482985</v>
       </c>
       <c r="R24" t="n">
-        <v>6989557</v>
+        <v>6989751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,6 +2905,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2939,7 +2939,7 @@
         <v>130341266</v>
       </c>
       <c r="B25" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>130341241</v>
       </c>
       <c r="B26" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>130341275</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B28" t="n">
-        <v>91774</v>
+        <v>79220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R28" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B29" t="n">
-        <v>79219</v>
+        <v>91775</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R29" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3429,7 +3429,7 @@
         <v>130341254</v>
       </c>
       <c r="B30" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>130341263</v>
       </c>
       <c r="B31" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>130341251</v>
       </c>
       <c r="B32" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130341272</v>
+        <v>130341273</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482934</v>
+        <v>483056</v>
       </c>
       <c r="R2" t="n">
-        <v>6989813</v>
+        <v>6989618</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130341273</v>
+        <v>130341272</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483056</v>
+        <v>482934</v>
       </c>
       <c r="R3" t="n">
-        <v>6989618</v>
+        <v>6989813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>130341240</v>
       </c>
       <c r="B4" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130341260</v>
       </c>
       <c r="B5" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130341252</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>130341271</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>130341261</v>
       </c>
       <c r="B8" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>130341253</v>
       </c>
       <c r="B9" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130341250</v>
       </c>
       <c r="B10" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130341239</v>
       </c>
       <c r="B11" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>130341249</v>
       </c>
       <c r="B12" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>130341264</v>
       </c>
       <c r="B13" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>130341269</v>
       </c>
       <c r="B14" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341247</v>
+        <v>130341267</v>
       </c>
       <c r="B15" t="n">
-        <v>57863</v>
+        <v>80326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482995</v>
+        <v>482997</v>
       </c>
       <c r="R15" t="n">
-        <v>6989739</v>
+        <v>6989532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2027,11 +2027,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341267</v>
+        <v>130341247</v>
       </c>
       <c r="B16" t="n">
-        <v>80325</v>
+        <v>57864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482997</v>
+        <v>482995</v>
       </c>
       <c r="R16" t="n">
-        <v>6989532</v>
+        <v>6989739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,7 +2158,7 @@
         <v>130341257</v>
       </c>
       <c r="B17" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>130341262</v>
       </c>
       <c r="B18" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>130341259</v>
       </c>
       <c r="B19" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>130341265</v>
       </c>
       <c r="B20" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130341268</v>
       </c>
       <c r="B21" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341274</v>
+        <v>130341258</v>
       </c>
       <c r="B22" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483054</v>
+        <v>483022</v>
       </c>
       <c r="R22" t="n">
-        <v>6989557</v>
+        <v>6989613</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341258</v>
+        <v>130341274</v>
       </c>
       <c r="B23" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483022</v>
+        <v>483054</v>
       </c>
       <c r="R23" t="n">
-        <v>6989613</v>
+        <v>6989557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2837,7 +2837,7 @@
         <v>130341248</v>
       </c>
       <c r="B24" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>130341266</v>
       </c>
       <c r="B25" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130341241</v>
+        <v>130341275</v>
       </c>
       <c r="B26" t="n">
-        <v>91775</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482982</v>
+        <v>483003</v>
       </c>
       <c r="R26" t="n">
-        <v>6989699</v>
+        <v>6989510</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130341275</v>
+        <v>130341241</v>
       </c>
       <c r="B27" t="n">
-        <v>79220</v>
+        <v>91776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483003</v>
+        <v>482982</v>
       </c>
       <c r="R27" t="n">
-        <v>6989510</v>
+        <v>6989699</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B28" t="n">
-        <v>79220</v>
+        <v>91776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R28" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B29" t="n">
-        <v>91775</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R29" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3429,7 +3429,7 @@
         <v>130341254</v>
       </c>
       <c r="B30" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>130341263</v>
       </c>
       <c r="B31" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>130341251</v>
       </c>
       <c r="B32" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R7" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B8" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R8" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130341275</v>
+        <v>130341241</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483003</v>
+        <v>482982</v>
       </c>
       <c r="R26" t="n">
-        <v>6989510</v>
+        <v>6989699</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130341241</v>
+        <v>130341275</v>
       </c>
       <c r="B27" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482982</v>
+        <v>483003</v>
       </c>
       <c r="R27" t="n">
-        <v>6989699</v>
+        <v>6989510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341269</v>
+        <v>130341267</v>
       </c>
       <c r="B14" t="n">
-        <v>91772</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483005</v>
+        <v>482997</v>
       </c>
       <c r="R14" t="n">
-        <v>6989508</v>
+        <v>6989532</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341267</v>
+        <v>130341247</v>
       </c>
       <c r="B15" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482997</v>
+        <v>482995</v>
       </c>
       <c r="R15" t="n">
-        <v>6989532</v>
+        <v>6989739</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2027,6 +2027,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341247</v>
+        <v>130341269</v>
       </c>
       <c r="B16" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482995</v>
+        <v>483005</v>
       </c>
       <c r="R16" t="n">
-        <v>6989739</v>
+        <v>6989508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130341241</v>
+        <v>130341275</v>
       </c>
       <c r="B26" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482982</v>
+        <v>483003</v>
       </c>
       <c r="R26" t="n">
-        <v>6989699</v>
+        <v>6989510</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130341275</v>
+        <v>130341241</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483003</v>
+        <v>482982</v>
       </c>
       <c r="R27" t="n">
-        <v>6989510</v>
+        <v>6989699</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341242</v>
+        <v>130341270</v>
       </c>
       <c r="B28" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483021</v>
+        <v>482930</v>
       </c>
       <c r="R28" t="n">
-        <v>6989677</v>
+        <v>6989844</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341270</v>
+        <v>130341242</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>482930</v>
+        <v>483021</v>
       </c>
       <c r="R29" t="n">
-        <v>6989844</v>
+        <v>6989677</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B7" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R7" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341271</v>
+        <v>130341261</v>
       </c>
       <c r="B8" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482987</v>
+        <v>482899</v>
       </c>
       <c r="R8" t="n">
-        <v>6989672</v>
+        <v>6989840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341267</v>
+        <v>130341247</v>
       </c>
       <c r="B14" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482997</v>
+        <v>482995</v>
       </c>
       <c r="R14" t="n">
-        <v>6989532</v>
+        <v>6989739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1930,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341247</v>
+        <v>130341269</v>
       </c>
       <c r="B15" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482995</v>
+        <v>483005</v>
       </c>
       <c r="R15" t="n">
-        <v>6989739</v>
+        <v>6989508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2027,11 +2032,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341269</v>
+        <v>130341267</v>
       </c>
       <c r="B16" t="n">
-        <v>91772</v>
+        <v>80326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483005</v>
+        <v>482997</v>
       </c>
       <c r="R16" t="n">
-        <v>6989508</v>
+        <v>6989532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341274</v>
+        <v>130341248</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483054</v>
+        <v>482985</v>
       </c>
       <c r="R23" t="n">
-        <v>6989557</v>
+        <v>6989751</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,6 +2808,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2834,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341248</v>
+        <v>130341274</v>
       </c>
       <c r="B24" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>482985</v>
+        <v>483054</v>
       </c>
       <c r="R24" t="n">
-        <v>6989751</v>
+        <v>6989557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2905,11 +2910,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130341275</v>
+        <v>130341241</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483003</v>
+        <v>482982</v>
       </c>
       <c r="R26" t="n">
-        <v>6989510</v>
+        <v>6989699</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130341241</v>
+        <v>130341275</v>
       </c>
       <c r="B27" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>482982</v>
+        <v>483003</v>
       </c>
       <c r="R27" t="n">
-        <v>6989699</v>
+        <v>6989510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130341273</v>
+        <v>130341269</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483056</v>
+        <v>483005</v>
       </c>
       <c r="R2" t="n">
-        <v>6989618</v>
+        <v>6989508</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130341272</v>
+        <v>130341239</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482934</v>
+        <v>482925</v>
       </c>
       <c r="R3" t="n">
-        <v>6989813</v>
+        <v>6989758</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>130341240</v>
       </c>
       <c r="B4" t="n">
-        <v>91776</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130341260</v>
+        <v>130341241</v>
       </c>
       <c r="B5" t="n">
-        <v>80326</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482960</v>
+        <v>482982</v>
       </c>
       <c r="R5" t="n">
-        <v>6989658</v>
+        <v>6989699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130341252</v>
+        <v>130341242</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483029</v>
+        <v>483021</v>
       </c>
       <c r="R6" t="n">
-        <v>6989662</v>
+        <v>6989677</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,14 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341271</v>
+        <v>130341270</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482987</v>
+        <v>482930</v>
       </c>
       <c r="R7" t="n">
-        <v>6989672</v>
+        <v>6989844</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341261</v>
+        <v>130341271</v>
       </c>
       <c r="B8" t="n">
-        <v>80326</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482899</v>
+        <v>482987</v>
       </c>
       <c r="R8" t="n">
-        <v>6989840</v>
+        <v>6989672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130341253</v>
+        <v>130341272</v>
       </c>
       <c r="B9" t="n">
-        <v>57864</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483089</v>
+        <v>482934</v>
       </c>
       <c r="R9" t="n">
-        <v>6989585</v>
+        <v>6989813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,11 +1430,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130341250</v>
+        <v>130341273</v>
       </c>
       <c r="B10" t="n">
-        <v>57864</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482916</v>
+        <v>483056</v>
       </c>
       <c r="R10" t="n">
-        <v>6989870</v>
+        <v>6989618</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1521,7 +1516,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Lockne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1532,11 +1527,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341239</v>
+        <v>130341274</v>
       </c>
       <c r="B11" t="n">
-        <v>91776</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482925</v>
+        <v>483054</v>
       </c>
       <c r="R11" t="n">
-        <v>6989758</v>
+        <v>6989557</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341249</v>
+        <v>130341275</v>
       </c>
       <c r="B12" t="n">
-        <v>57864</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482941</v>
+        <v>483003</v>
       </c>
       <c r="R12" t="n">
-        <v>6989821</v>
+        <v>6989510</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1721,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130341264</v>
+        <v>122386324</v>
       </c>
       <c r="B13" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483088</v>
+        <v>483051</v>
       </c>
       <c r="R13" t="n">
-        <v>6989589</v>
+        <v>6989494</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1827,12 +1812,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130341247</v>
+        <v>130341257</v>
       </c>
       <c r="B14" t="n">
-        <v>57864</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482995</v>
+        <v>483028</v>
       </c>
       <c r="R14" t="n">
-        <v>6989739</v>
+        <v>6989627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,11 +1915,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1961,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130341269</v>
+        <v>130341258</v>
       </c>
       <c r="B15" t="n">
-        <v>91772</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1996,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483005</v>
+        <v>483022</v>
       </c>
       <c r="R15" t="n">
-        <v>6989508</v>
+        <v>6989613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130341267</v>
+        <v>130341259</v>
       </c>
       <c r="B16" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2093,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>482997</v>
+        <v>483019</v>
       </c>
       <c r="R16" t="n">
-        <v>6989532</v>
+        <v>6989574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130341257</v>
+        <v>130341260</v>
       </c>
       <c r="B17" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2190,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483028</v>
+        <v>482960</v>
       </c>
       <c r="R17" t="n">
-        <v>6989627</v>
+        <v>6989658</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130341262</v>
+        <v>130341261</v>
       </c>
       <c r="B18" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483057</v>
+        <v>482899</v>
       </c>
       <c r="R18" t="n">
-        <v>6989643</v>
+        <v>6989840</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2349,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130341259</v>
+        <v>130341262</v>
       </c>
       <c r="B19" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2384,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483019</v>
+        <v>483057</v>
       </c>
       <c r="R19" t="n">
-        <v>6989574</v>
+        <v>6989643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130341265</v>
+        <v>130341263</v>
       </c>
       <c r="B20" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483039</v>
+        <v>483067</v>
       </c>
       <c r="R20" t="n">
-        <v>6989557</v>
+        <v>6989609</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2543,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130341268</v>
+        <v>130341264</v>
       </c>
       <c r="B21" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>482923</v>
+        <v>483088</v>
       </c>
       <c r="R21" t="n">
-        <v>6989690</v>
+        <v>6989589</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2640,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130341258</v>
+        <v>130341265</v>
       </c>
       <c r="B22" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2675,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483022</v>
+        <v>483039</v>
       </c>
       <c r="R22" t="n">
-        <v>6989613</v>
+        <v>6989557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130341248</v>
+        <v>130341266</v>
       </c>
       <c r="B23" t="n">
-        <v>57864</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>482985</v>
+        <v>483025</v>
       </c>
       <c r="R23" t="n">
-        <v>6989751</v>
+        <v>6989564</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,11 +2788,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341274</v>
+        <v>130341267</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483054</v>
+        <v>482997</v>
       </c>
       <c r="R24" t="n">
-        <v>6989557</v>
+        <v>6989532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130341266</v>
+        <v>130341268</v>
       </c>
       <c r="B25" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2971,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483025</v>
+        <v>482923</v>
       </c>
       <c r="R25" t="n">
-        <v>6989564</v>
+        <v>6989690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130341241</v>
+        <v>122386318</v>
       </c>
       <c r="B26" t="n">
-        <v>91776</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3019,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>482982</v>
+        <v>482996</v>
       </c>
       <c r="R26" t="n">
-        <v>6989699</v>
+        <v>6989426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3098,12 +3073,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3130,10 +3110,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130341275</v>
+        <v>130341244</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483003</v>
+        <v>483032</v>
       </c>
       <c r="R27" t="n">
-        <v>6989510</v>
+        <v>6989701</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3190,7 +3170,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Lockne</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3201,6 +3181,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3227,10 +3212,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130341270</v>
+        <v>130341245</v>
       </c>
       <c r="B28" t="n">
-        <v>79221</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3223,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3247,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>482930</v>
+        <v>483019</v>
       </c>
       <c r="R28" t="n">
-        <v>6989844</v>
+        <v>6989712</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3287,7 +3272,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Lockne</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3302,7 +3287,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3314,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130341242</v>
+        <v>130341246</v>
       </c>
       <c r="B29" t="n">
-        <v>91776</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3325,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483021</v>
+        <v>483013</v>
       </c>
       <c r="R29" t="n">
-        <v>6989677</v>
+        <v>6989724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3389,7 +3374,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Lockne</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3400,6 +3385,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3426,10 +3416,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130341254</v>
+        <v>130341247</v>
       </c>
       <c r="B30" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3461,10 +3451,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>482908</v>
+        <v>482995</v>
       </c>
       <c r="R30" t="n">
-        <v>6989866</v>
+        <v>6989739</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3501,7 +3491,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3528,10 +3518,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130341263</v>
+        <v>130341248</v>
       </c>
       <c r="B31" t="n">
-        <v>80326</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,21 +3529,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3563,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483067</v>
+        <v>482985</v>
       </c>
       <c r="R31" t="n">
-        <v>6989609</v>
+        <v>6989751</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,6 +3589,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3625,10 +3620,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130341251</v>
+        <v>130341249</v>
       </c>
       <c r="B32" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>482998</v>
+        <v>482941</v>
       </c>
       <c r="R32" t="n">
-        <v>6989561</v>
+        <v>6989821</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3724,6 +3719,516 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130341250</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Låshålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>482916</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6989870</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130341251</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Låshålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>482998</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6989561</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130341252</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Låshålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>483029</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6989662</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130341253</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Låshålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>483089</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6989585</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130341254</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Låshålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>482908</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6989866</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58372-2025 artfynd.xlsx
+++ b/artfynd/A 58372-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341269</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341239</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341240</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341241</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341242</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341270</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341271</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341272</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341273</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341274</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341275</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386324</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341257</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341258</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341259</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341260</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341261</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341262</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341263</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341264</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341265</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341266</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341267</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341268</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122386318</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3209,6 +3339,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341244</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3311,6 +3446,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341245</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3413,6 +3553,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341246</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3515,6 +3660,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341247</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3617,6 +3767,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341248</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3719,6 +3874,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341249</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3821,6 +3981,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341250</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3923,6 +4088,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341251</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4025,6 +4195,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341252</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4127,6 +4302,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341253</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4229,8 +4409,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341254</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>